--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1224,6 +1224,230 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>SIO</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/sio.owl</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>geographic region [SIO:000414]; geolegal region [SIO:000413]; geopolitical region [SIO:000415]</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>NCIT</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/ncit.owl</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>agitation [NCIT:C79530]; thalamus [NCIT:C12459]</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/hp.owl</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>aortic stiffness [HP:0030965]</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>CHEBI</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/chebi.owl</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>cotinine [CHEBI:68641]; acetaldehyde [CHEBI:15343]; acrolein [CHEBI:15368]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; acetylcysteine [CHEBI:22198]; aripiprazole [CHEBI:31236]; methanol [CHEBI:17790]</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>UBERON</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/uberon.owl</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>death [UBERON:0035944]</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ADDICTO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/addicto.owl</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>substance-induced anxiety disorder [ADDICTO:0001039]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SDGIO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/sdgio.owl</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>unemployed status [SDGIO:00010026]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>GSSO</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/gsso.owl</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>advocacy organisation [GSSO:005379]; health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]; money [GSSO:010609]</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2E6A852E-39C3-F145-A981-5BDB6ABE4DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B89639D-F332-E245-BF8C-D73690A4D1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="1200" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1680" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Imports" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="112">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -310,15 +310,6 @@
     <t>Life cycle temporal boundary [UBERON:0035943]; Death [UBERON:035944]; death stage [UBERON:0000071]</t>
   </si>
   <si>
-    <t>AFP</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/afp.owl</t>
-  </si>
-  <si>
-    <t>measurement [AFP:0000225]</t>
-  </si>
-  <si>
     <t>SIO</t>
   </si>
   <si>
@@ -356,15 +347,6 @@
   </si>
   <si>
     <t>death [UBERON:0035944]</t>
-  </si>
-  <si>
-    <t>SDGIO</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/sdgio.owl</t>
-  </si>
-  <si>
-    <t>unemployed status [SDGIO:00010026]</t>
   </si>
   <si>
     <t>GSSO</t>
@@ -747,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1280,13 +1262,13 @@
         <v>105</v>
       </c>
       <c r="B31" t="s">
+        <v>23</v>
+      </c>
+      <c r="C31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
         <v>106</v>
-      </c>
-      <c r="C31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" t="s">
-        <v>107</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -1294,16 +1276,16 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B32" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
         <v>108</v>
-      </c>
-      <c r="B32" t="s">
-        <v>23</v>
-      </c>
-      <c r="C32" t="s">
-        <v>27</v>
-      </c>
-      <c r="D32" t="s">
-        <v>109</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
@@ -1311,10 +1293,10 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" t="s">
         <v>110</v>
-      </c>
-      <c r="B33" t="s">
-        <v>90</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
@@ -1323,40 +1305,6 @@
         <v>111</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>112</v>
-      </c>
-      <c r="B34" t="s">
-        <v>113</v>
-      </c>
-      <c r="C34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" t="s">
-        <v>114</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" t="s">
-        <v>116</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" t="s">
-        <v>117</v>
-      </c>
-      <c r="E35" t="s">
         <v>10</v>
       </c>
     </row>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B89639D-F332-E245-BF8C-D73690A4D1B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563C8413-7251-B84B-B14E-7FCFDBF22938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1680" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="109">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -308,15 +308,6 @@
   </si>
   <si>
     <t>Life cycle temporal boundary [UBERON:0035943]; Death [UBERON:035944]; death stage [UBERON:0000071]</t>
-  </si>
-  <si>
-    <t>SIO</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/sio.owl</t>
-  </si>
-  <si>
-    <t>geographic region [SIO:000414]; geolegal region [SIO:000413]; geopolitical region [SIO:000415]</t>
   </si>
   <si>
     <t>NCIT</t>
@@ -729,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1245,13 +1236,13 @@
         <v>102</v>
       </c>
       <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
         <v>103</v>
-      </c>
-      <c r="C30" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" t="s">
-        <v>104</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -1259,16 +1250,16 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
+        <v>104</v>
+      </c>
+      <c r="B31" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" t="s">
         <v>105</v>
-      </c>
-      <c r="B31" t="s">
-        <v>23</v>
-      </c>
-      <c r="C31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" t="s">
-        <v>106</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -1276,10 +1267,10 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" t="s">
         <v>107</v>
-      </c>
-      <c r="B32" t="s">
-        <v>90</v>
       </c>
       <c r="C32" t="s">
         <v>8</v>
@@ -1288,23 +1279,6 @@
         <v>108</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" t="s">
-        <v>109</v>
-      </c>
-      <c r="B33" t="s">
-        <v>110</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" t="s">
-        <v>111</v>
-      </c>
-      <c r="E33" t="s">
         <v>10</v>
       </c>
     </row>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{563C8413-7251-B84B-B14E-7FCFDBF22938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF6AE9-6C58-7E48-BA39-37D67155C59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1680" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -346,7 +346,7 @@
     <t>http://purl.obolibrary.org/obo/gsso.owl</t>
   </si>
   <si>
-    <t>advocacy organisation [GSSO:005379]; health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]; money [GSSO:010609]</t>
+    <t>advocacy organisation [GSSO:005379]; health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]</t>
   </si>
 </sst>
 </file>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CCF6AE9-6C58-7E48-BA39-37D67155C59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C19C7846-0687-7640-8479-1F7290795A4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1440" yWindow="1680" windowWidth="25600" windowHeight="14580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -834,7 +834,7 @@
         <v>25</v>
       </c>
       <c r="E6" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="388" customHeight="1" x14ac:dyDescent="0.2">
@@ -851,7 +851,7 @@
         <v>28</v>
       </c>
       <c r="E7" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2"/>
     </row>
@@ -869,7 +869,7 @@
         <v>31</v>
       </c>
       <c r="E8" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F8" s="2"/>
     </row>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1358,7 +1358,6 @@
           <t>all</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>cotinine [CHEBI:68641]; acetaldehyde [CHEBI:15343]; acrolein [CHEBI:15368]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; acetylcysteine [CHEBI:22198]; aripiprazole [CHEBI:31236]; methanol [CHEBI:17790]</t>
+          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; acrylonitrile [CHEBI:28217]; methanol [CHEBI:17790]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; acrylonitrile [CHEBI:28217]; methanol [CHEBI:17790]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
+          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
+          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; acrylonitrile [CHEBI:28217]; methanol [CHEBI:17790]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; acrylonitrile [CHEBI:28217]; methanol [CHEBI:17790]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
+          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
+          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
+          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; codeine [CHEBI:38164]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; codeine [CHEBI:38164]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; acrolein [CHEBI:15368]</t>
+          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; codeine [CHEBI:38164]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; drug role [CHEBI:23888]; acrolein [CHEBI:15368]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -564,7 +564,7 @@
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
-          <t>process [BFO:0000015]; object aggregate [BFO:0000027]; role [BFO:0000023]; disposition [BFO:0000016]; object [BFO:0000030]; process profile [BFO:0000144]; site [BFO:0000029]; occurrent [BFO:0000003]; process boundary [BFO:0000035]; temporal region [BFO:0000008]; fiat object part [﻿BFO:0000024]; immaterial entity [BFO:0000141]; ﻿spatial region [BFO:0000006];specifically dependent continuant [BFO:0000020]</t>
+          <t>﻿spatial region [BFO:0000006]; object [BFO:0000030]; occurrent [BFO:0000003]; fiat object part [﻿BFO:0000024]; process [BFO:0000015]; site [BFO:0000029]; role [BFO:0000023]; fiat object [BFO:0000024]; immaterial entity [BFO:0000141]; object aggregate [BFO:0000027]; temporal region [BFO:0000008]; disposition [BFO:0000016]; process boundary [BFO:0000035]; process profile [BFO:0000144]; specifically dependent continuant [BFO:0000020]</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; CB2 receptor agonist [CHEBI:73417]; antipsychotic drug [CHEBI:35476]; methanol [CHEBI:17790]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; codeine [CHEBI:38164]; aripiprazole [CHEBI:31236]; acetylcysteine [CHEBI:22198]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; drug role [CHEBI:23888]; acrolein [CHEBI:15368]</t>
+          <t>CB2 receptor agonist [CHEBI:73417]; methanol [CHEBI:17790]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; methadrone [CHEBI:59331]; aripiprazole [CHEBI:31236]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; drug role [CHEBI:23888]; acrolein [CHEBI:15368]; 3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; antipsychotic drug [CHEBI:35476]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; codeine [CHEBI:38164]; acetylcysteine [CHEBI:22198]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>advocacy organisation [GSSO:005379]; health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]</t>
+          <t>health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]; advocacy organisation [GSSO:005379]; money [GSSO:010609]</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1269,7 +1269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>CB2 receptor agonist [CHEBI:73417]; methanol [CHEBI:17790]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; methadrone [CHEBI:59331]; aripiprazole [CHEBI:31236]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; drug role [CHEBI:23888]; acrolein [CHEBI:15368]; 3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; antipsychotic drug [CHEBI:35476]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; codeine [CHEBI:38164]; acetylcysteine [CHEBI:22198]</t>
+          <t>CB2 receptor agonist [CHEBI:73417]; methanol [CHEBI:17790]; acetaldehyde [CHEBI:15343]; carbon-monoxide [CHEBI:17245]; methadrone [CHEBI:59331]; aripiprazole [CHEBI:31236]; alcohol dehydrogenase 1B [CHEBI:50269]; cotinine [CHEBI:68641]; drug role [CHEBI:23888]; acrolein [CHEBI:15368]; 3,4-Methylenedioxymethamphetamine [CHEBI:1391]; 4-(methylnitrosamino)-1-(3-pyridyl)-1-butanol [CHEBI:82569]; tetrahydrocannabinol [CHEBI:66964]; antipsychotic drug [CHEBI:35476]; acrylonitrile [CHEBI:28217]; metabolite [CHEBI:25212]; codeine [CHEBI:38164]; acetylcysteine [CHEBI:22198]</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -917,7 +917,7 @@
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
-          <t>Credible interval [OBCS:0000071]; Mortality ratio [OBCS:0000150]; model [OBCS:0000035]</t>
+          <t>Mortality ratio [OBCS:0000150]; Credible interval [OBCS:0000071]; mortality ratio [OBCS:0000150]; model [OBCS:0000035]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1359,6 +1359,34 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>SDGIO</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/sdgio.owl</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>unemployed status [SDGIO:00010026]</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1385,7 +1385,6 @@
           <t>all</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -1386,6 +1386,34 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>SIO</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/sio.owl</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>entity [BFO:0000001]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>geographic region [SIO:000414]</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>geographic region [SIO:000414]</t>
+          <t>geolegal region [SIO:000413]; geographic region [SIO:000414]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1412,7 +1412,6 @@
           <t>all</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -1404,7 +1404,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>geolegal region [SIO:000413]; geographic region [SIO:000414]</t>
+          <t>geographic region [SIO:000414]; geolegal region [SIO:000413]; geopolitical region [SIO:000415]</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA698F29-5460-0449-8BE6-7F093FDA8751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E573E187-D862-E640-BC2B-3E036858D535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="115">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -349,12 +349,6 @@
     <t>health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]; advocacy organisation [GSSO:005379]; money [GSSO:010609]</t>
   </si>
   <si>
-    <t>AFP</t>
-  </si>
-  <si>
-    <t>measurement [AFP:0000225]</t>
-  </si>
-  <si>
     <t>SDGIO</t>
   </si>
   <si>
@@ -365,9 +359,6 @@
   </si>
   <si>
     <t>geographic region [SIO:000414]; geolegal region [SIO:000413]; geopolitical region [SIO:000415]</t>
-  </si>
-  <si>
-    <t>http://purl.allotrope.org/voc/afo/merged/REC/2024/03/merged-without-qudt-and-inferred</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/SDG-InterfaceOntology/sdgio/master/sdgio.owl</t>
@@ -747,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1314,7 +1305,7 @@
         <v>109</v>
       </c>
       <c r="B33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C33" t="s">
         <v>8</v>
@@ -1331,7 +1322,7 @@
         <v>111</v>
       </c>
       <c r="B34" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
         <v>8</v>
@@ -1340,23 +1331,6 @@
         <v>112</v>
       </c>
       <c r="E34" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" t="s">
-        <v>113</v>
-      </c>
-      <c r="B35" t="s">
-        <v>117</v>
-      </c>
-      <c r="C35" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" t="s">
-        <v>114</v>
-      </c>
-      <c r="E35" t="s">
         <v>10</v>
       </c>
     </row>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E573E187-D862-E640-BC2B-3E036858D535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF362277-76DC-ED49-B734-2C6B738092D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="117">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -365,6 +365,12 @@
   </si>
   <si>
     <t>http://semanticscience.org/ontology/sio.owl</t>
+  </si>
+  <si>
+    <t>"SDGIO: http://purl.unep.org/sdg/SDGIO_"</t>
+  </si>
+  <si>
+    <t>geographic region [SIO:000414]</t>
   </si>
 </sst>
 </file>
@@ -1300,7 +1306,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>109</v>
       </c>
@@ -1316,8 +1322,11 @@
       <c r="E33" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F33" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>111</v>
       </c>
@@ -1325,7 +1334,7 @@
         <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>8</v>
+        <v>116</v>
       </c>
       <c r="D34" t="s">
         <v>112</v>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF362277-76DC-ED49-B734-2C6B738092D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277C487D-0E44-3A47-832C-858C89348E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -371,6 +371,9 @@
   </si>
   <si>
     <t>geographic region [SIO:000414]</t>
+  </si>
+  <si>
+    <t>"SIO: http://semanticscience.org/resource/SIO_"</t>
   </si>
 </sst>
 </file>
@@ -1342,6 +1345,9 @@
       <c r="E34" t="s">
         <v>10</v>
       </c>
+      <c r="F34" t="s">
+        <v>117</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/imports/External_Imports.xlsx
+++ b/imports/External_Imports.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bgehrk/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277C487D-0E44-3A47-832C-858C89348E73}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FD2F2A-F3EE-DD4F-AB4B-3D5F68169322}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="16840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="115">
   <si>
     <t>Ontology ID</t>
   </si>
@@ -338,15 +338,6 @@
   </si>
   <si>
     <t>death [UBERON:0035944]</t>
-  </si>
-  <si>
-    <t>GSSO</t>
-  </si>
-  <si>
-    <t>http://purl.obolibrary.org/obo/gsso.owl</t>
-  </si>
-  <si>
-    <t>health organisation [GSSO:007328]; human rights organisation [GSSO:003501]; non-profit organisation [GSSO:004615]; advocacy organisation [GSSO:005379]; money [GSSO:010609]</t>
   </si>
   <si>
     <t>SDGIO</t>
@@ -747,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="19" customWidth="1"/>
@@ -1297,56 +1288,39 @@
         <v>106</v>
       </c>
       <c r="B32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
         <v>107</v>
       </c>
-      <c r="C32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" t="s">
-        <v>108</v>
-      </c>
       <c r="E32" t="s">
         <v>10</v>
+      </c>
+      <c r="F32" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
+        <v>108</v>
+      </c>
+      <c r="B33" t="s">
+        <v>111</v>
+      </c>
+      <c r="C33" t="s">
+        <v>113</v>
+      </c>
+      <c r="D33" t="s">
         <v>109</v>
       </c>
-      <c r="B33" t="s">
-        <v>113</v>
-      </c>
-      <c r="C33" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" t="s">
-        <v>110</v>
-      </c>
       <c r="E33" t="s">
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
-        <v>111</v>
-      </c>
-      <c r="B34" t="s">
         <v>114</v>
-      </c>
-      <c r="C34" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" t="s">
-        <v>112</v>
-      </c>
-      <c r="E34" t="s">
-        <v>10</v>
-      </c>
-      <c r="F34" t="s">
-        <v>117</v>
       </c>
     </row>
   </sheetData>
